--- a/education_surveys/041_father_s_day_questionnaire--education_surveys.xlsx
+++ b/education_surveys/041_father_s_day_questionnaire--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>what_does_dad_like</t>
+          <t>what_does_dad_like_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What does dad like</t>
+          <t>What Does Dad Like 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What does dad love most?</t>
+          <t>What does dad love most? (2)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>best_gift_for_dad</t>
+          <t>best_gift_for_dad_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Best gift for dad</t>
+          <t>Best Gift For Dad 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Father's favorite food</t>
+          <t>Father's favorite food (2)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>best_gift_for_dad_choices</t>
+          <t>best_gift_for_dad_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1712,7 +1712,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>best_gift_for_dad_choices</t>
+          <t>best_gift_for_dad_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1729,7 +1729,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>best_gift_for_dad_choices</t>
+          <t>best_gift_for_dad_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
